--- a/見積書.xlsx
+++ b/見積書.xlsx
@@ -11,7 +11,7 @@
     <sheet name="見積書" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">見積書!$A$1:$G$43</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">見積書!$A$1:$G$36</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,9 +23,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t xml:space="preserve">御 見 積 書</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※青字のセルが入力項目です（宛先・件名・明細・税率など）。明細は最大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Meiryo UI"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行。この列は印刷範囲外です。</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">株式会社〇〇〇〇　御中</t>
@@ -171,72 +201,6 @@
   <si>
     <t xml:space="preserve">合　計（税込）</t>
   </si>
-  <si>
-    <t xml:space="preserve">・お支払条件：納品月末締め、翌月末払い（銀行振込・振込手数料はお客様負担）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">・納期：ご発注後〇週間</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・本見積書の有効期限は発行日より</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Meiryo UI"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日間です。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※青字のセルが入力項目です（宛先・件名・明細・税率など）。明細は最大</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF808080"/>
-        <rFont val="Meiryo UI"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF808080"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">行。</t>
-    </r>
-  </si>
 </sst>
 </file>
 
@@ -280,6 +244,19 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Meiryo UI"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="14"/>
       <color rgb="FF0000FF"/>
@@ -371,19 +348,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Meiryo UI"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF808080"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF808080"/>
       <name val="Meiryo UI"/>
       <family val="0"/>
       <charset val="1"/>
@@ -481,7 +445,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -490,23 +454,35 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -514,71 +490,63 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -586,23 +554,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -676,6 +632,48 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>828360</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>361440</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1180800" cy="361440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -858,7 +856,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -880,535 +878,483 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
+      <c r="I1" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="E3" s="3" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="E3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="F3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="5" t="n">
+      <c r="E4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="6" t="n">
         <v>46318</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="A5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="E5" s="3" t="s">
+      <c r="B5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="C5" s="8"/>
+      <c r="E5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="9" t="n">
         <f aca="false">F4+30</f>
         <v>46348</v>
       </c>
-      <c r="G5" s="8"/>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
+      <c r="A6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
+      <c r="E7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
+      <c r="E8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="11" t="n">
+      <c r="A9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="12" t="n">
         <f aca="false">F36</f>
         <v>594000</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="13"/>
-      <c r="E10" s="4" t="s">
+      <c r="A10" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
+      <c r="B10" s="14"/>
+      <c r="E10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
+      <c r="E11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="15" t="s">
+      <c r="A13" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="B13" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="C13" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="D13" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="E13" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="F13" s="16" t="s">
         <v>22</v>
       </c>
+      <c r="G13" s="16" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="n">
+      <c r="A14" s="17" t="n">
         <f aca="false">IF(B14="","",ROW()-13)</f>
         <v>1</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="18" t="n">
+      <c r="B14" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="18" t="n">
+      <c r="D14" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="19" t="n">
         <v>300000</v>
       </c>
-      <c r="F14" s="20" t="n">
+      <c r="F14" s="21" t="n">
         <f aca="false">IF(OR(C14="",E14=""),"",ROUND(C14*E14,0))</f>
         <v>300000</v>
       </c>
-      <c r="G14" s="21" t="s">
-        <v>25</v>
+      <c r="G14" s="22" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16" t="n">
+      <c r="A15" s="17" t="n">
         <f aca="false">IF(B15="","",ROW()-13)</f>
         <v>2</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="18" t="n">
+      <c r="B15" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="D15" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="18" t="n">
+      <c r="D15" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="19" t="n">
         <v>20000</v>
       </c>
-      <c r="F15" s="20" t="n">
+      <c r="F15" s="21" t="n">
         <f aca="false">IF(OR(C15="",E15=""),"",ROUND(C15*E15,0))</f>
         <v>240000</v>
       </c>
-      <c r="G15" s="21"/>
+      <c r="G15" s="22"/>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="str">
+      <c r="A16" s="17" t="str">
         <f aca="false">IF(B16="","",ROW()-13)</f>
         <v/>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="20" t="str">
+      <c r="B16" s="18"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="21" t="str">
         <f aca="false">IF(OR(C16="",E16=""),"",ROUND(C16*E16,0))</f>
         <v/>
       </c>
-      <c r="G16" s="21"/>
+      <c r="G16" s="22"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="str">
+      <c r="A17" s="17" t="str">
         <f aca="false">IF(B17="","",ROW()-13)</f>
         <v/>
       </c>
-      <c r="B17" s="17"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="20" t="str">
+      <c r="B17" s="18"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="21" t="str">
         <f aca="false">IF(OR(C17="",E17=""),"",ROUND(C17*E17,0))</f>
         <v/>
       </c>
-      <c r="G17" s="21"/>
+      <c r="G17" s="22"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="str">
+      <c r="A18" s="17" t="str">
         <f aca="false">IF(B18="","",ROW()-13)</f>
         <v/>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="20" t="str">
+      <c r="B18" s="18"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="21" t="str">
         <f aca="false">IF(OR(C18="",E18=""),"",ROUND(C18*E18,0))</f>
         <v/>
       </c>
-      <c r="G18" s="21"/>
+      <c r="G18" s="22"/>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="str">
+      <c r="A19" s="17" t="str">
         <f aca="false">IF(B19="","",ROW()-13)</f>
         <v/>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="20" t="str">
+      <c r="B19" s="18"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="21" t="str">
         <f aca="false">IF(OR(C19="",E19=""),"",ROUND(C19*E19,0))</f>
         <v/>
       </c>
-      <c r="G19" s="21"/>
+      <c r="G19" s="22"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="str">
+      <c r="A20" s="17" t="str">
         <f aca="false">IF(B20="","",ROW()-13)</f>
         <v/>
       </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="20" t="str">
+      <c r="B20" s="18"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="21" t="str">
         <f aca="false">IF(OR(C20="",E20=""),"",ROUND(C20*E20,0))</f>
         <v/>
       </c>
-      <c r="G20" s="21"/>
+      <c r="G20" s="22"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="str">
+      <c r="A21" s="17" t="str">
         <f aca="false">IF(B21="","",ROW()-13)</f>
         <v/>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="20" t="str">
+      <c r="B21" s="18"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="21" t="str">
         <f aca="false">IF(OR(C21="",E21=""),"",ROUND(C21*E21,0))</f>
         <v/>
       </c>
-      <c r="G21" s="21"/>
+      <c r="G21" s="22"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16" t="str">
+      <c r="A22" s="17" t="str">
         <f aca="false">IF(B22="","",ROW()-13)</f>
         <v/>
       </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="20" t="str">
+      <c r="B22" s="18"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="21" t="str">
         <f aca="false">IF(OR(C22="",E22=""),"",ROUND(C22*E22,0))</f>
         <v/>
       </c>
-      <c r="G22" s="21"/>
+      <c r="G22" s="22"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="16" t="str">
+      <c r="A23" s="17" t="str">
         <f aca="false">IF(B23="","",ROW()-13)</f>
         <v/>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="20" t="str">
+      <c r="B23" s="18"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="21" t="str">
         <f aca="false">IF(OR(C23="",E23=""),"",ROUND(C23*E23,0))</f>
         <v/>
       </c>
-      <c r="G23" s="21"/>
+      <c r="G23" s="22"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16" t="str">
+      <c r="A24" s="17" t="str">
         <f aca="false">IF(B24="","",ROW()-13)</f>
         <v/>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="20" t="str">
+      <c r="B24" s="18"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="21" t="str">
         <f aca="false">IF(OR(C24="",E24=""),"",ROUND(C24*E24,0))</f>
         <v/>
       </c>
-      <c r="G24" s="21"/>
+      <c r="G24" s="22"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16" t="str">
+      <c r="A25" s="17" t="str">
         <f aca="false">IF(B25="","",ROW()-13)</f>
         <v/>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="20" t="str">
+      <c r="B25" s="18"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="21" t="str">
         <f aca="false">IF(OR(C25="",E25=""),"",ROUND(C25*E25,0))</f>
         <v/>
       </c>
-      <c r="G25" s="21"/>
+      <c r="G25" s="22"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="16" t="str">
+      <c r="A26" s="17" t="str">
         <f aca="false">IF(B26="","",ROW()-13)</f>
         <v/>
       </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="20" t="str">
+      <c r="B26" s="18"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="21" t="str">
         <f aca="false">IF(OR(C26="",E26=""),"",ROUND(C26*E26,0))</f>
         <v/>
       </c>
-      <c r="G26" s="21"/>
+      <c r="G26" s="22"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="16" t="str">
+      <c r="A27" s="17" t="str">
         <f aca="false">IF(B27="","",ROW()-13)</f>
         <v/>
       </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="20" t="str">
+      <c r="B27" s="18"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="21" t="str">
         <f aca="false">IF(OR(C27="",E27=""),"",ROUND(C27*E27,0))</f>
         <v/>
       </c>
-      <c r="G27" s="21"/>
+      <c r="G27" s="22"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="16" t="str">
+      <c r="A28" s="17" t="str">
         <f aca="false">IF(B28="","",ROW()-13)</f>
         <v/>
       </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="20" t="str">
+      <c r="B28" s="18"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="21" t="str">
         <f aca="false">IF(OR(C28="",E28=""),"",ROUND(C28*E28,0))</f>
         <v/>
       </c>
-      <c r="G28" s="21"/>
+      <c r="G28" s="22"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="16" t="str">
+      <c r="A29" s="17" t="str">
         <f aca="false">IF(B29="","",ROW()-13)</f>
         <v/>
       </c>
-      <c r="B29" s="17"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="20" t="str">
+      <c r="B29" s="18"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="21" t="str">
         <f aca="false">IF(OR(C29="",E29=""),"",ROUND(C29*E29,0))</f>
         <v/>
       </c>
-      <c r="G29" s="21"/>
+      <c r="G29" s="22"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="16" t="str">
+      <c r="A30" s="17" t="str">
         <f aca="false">IF(B30="","",ROW()-13)</f>
         <v/>
       </c>
-      <c r="B30" s="17"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="20" t="str">
+      <c r="B30" s="18"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="21" t="str">
         <f aca="false">IF(OR(C30="",E30=""),"",ROUND(C30*E30,0))</f>
         <v/>
       </c>
-      <c r="G30" s="21"/>
+      <c r="G30" s="22"/>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="16" t="str">
+      <c r="A31" s="17" t="str">
         <f aca="false">IF(B31="","",ROW()-13)</f>
         <v/>
       </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="20" t="str">
+      <c r="B31" s="18"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="21" t="str">
         <f aca="false">IF(OR(C31="",E31=""),"",ROUND(C31*E31,0))</f>
         <v/>
       </c>
-      <c r="G31" s="21"/>
+      <c r="G31" s="22"/>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="16" t="str">
+      <c r="A32" s="17" t="str">
         <f aca="false">IF(B32="","",ROW()-13)</f>
         <v/>
       </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="20" t="str">
+      <c r="B32" s="18"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="21" t="str">
         <f aca="false">IF(OR(C32="",E32=""),"",ROUND(C32*E32,0))</f>
         <v/>
       </c>
-      <c r="G32" s="21"/>
+      <c r="G32" s="22"/>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="16" t="str">
+      <c r="A33" s="17" t="str">
         <f aca="false">IF(B33="","",ROW()-13)</f>
         <v/>
       </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="20" t="str">
+      <c r="B33" s="18"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="21" t="str">
         <f aca="false">IF(OR(C33="",E33=""),"",ROUND(C33*E33,0))</f>
         <v/>
       </c>
-      <c r="G33" s="21"/>
+      <c r="G33" s="22"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D34" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="E34" s="23"/>
-      <c r="F34" s="24" t="n">
+      <c r="D34" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="E34" s="24"/>
+      <c r="F34" s="25" t="n">
         <f aca="false">SUM(F14:F33)</f>
         <v>540000</v>
       </c>
-      <c r="G34" s="25"/>
+      <c r="G34" s="26"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D35" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="E35" s="23"/>
-      <c r="F35" s="26" t="n">
+      <c r="D35" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="24"/>
+      <c r="F35" s="27" t="n">
         <f aca="false">ROUND(F34*G35,0)</f>
         <v>54000</v>
       </c>
-      <c r="G35" s="27" t="n">
+      <c r="G35" s="28" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D36" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E36" s="23"/>
-      <c r="F36" s="24" t="n">
+      <c r="D36" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E36" s="24"/>
+      <c r="F36" s="25" t="n">
         <f aca="false">F34+F35</f>
         <v>594000</v>
       </c>
-      <c r="G36" s="25"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B38" s="29"/>
-      <c r="C38" s="29"/>
-      <c r="D38" s="29"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29"/>
-      <c r="G38" s="29"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-    </row>
-    <row r="41" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-    </row>
-    <row r="43" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
+      <c r="G36" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="18">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="F3:G3"/>
@@ -1427,10 +1373,6 @@
     <mergeCell ref="D34:E34"/>
     <mergeCell ref="D35:E35"/>
     <mergeCell ref="D36:E36"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A43:G43"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.6" right="0.6" top="0.7" bottom="0.7" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1439,5 +1381,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>